--- a/order_forms/032_healthy_shake_request_form--order_forms.xlsx
+++ b/order_forms/032_healthy_shake_request_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -738,8 +738,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -767,12 +767,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'address_type':_'home',_'value':_'home'}</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'address_type': 'Home', 'value': 'Home'}</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -784,12 +784,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'address_type':_'work',_'value':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'address_type': 'Work', 'value': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -801,12 +801,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'shake_type':_'mango_madness',_'value':_'mango_madness',_'suboptions':_[{'size':_'small',_'value':_'small'},_{'size':_'medium',_'value':_'medium'},_{'size':_'large',_'value':_'large'}]}</t>
+          <t>mango_madness</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'shake_type': 'Mango Madness', 'value': 'Mango Madness', 'suboptions': [{'size': 'Small', 'value': 'Small'}, {'size': 'Medium', 'value': 'Medium'}, {'size': 'Large', 'value': 'Large'}]}</t>
+          <t>Mango Madness</t>
         </is>
       </c>
     </row>
@@ -835,12 +835,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'delivery_type':_'pickup',_'value':_'pickup'}</t>
+          <t>pickup</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'delivery_type': 'Pickup', 'value': 'Pickup'}</t>
+          <t>Pickup</t>
         </is>
       </c>
     </row>
@@ -852,12 +852,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'delivery_type':_'delivery',_'value':_'delivery'}</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'delivery_type': 'Delivery', 'value': 'Delivery'}</t>
+          <t>Delivery</t>
         </is>
       </c>
     </row>
